--- a/www/flightdata/xlsx/eoss-344.xlsx
+++ b/www/flightdata/xlsx/eoss-344.xlsx
@@ -3423,7 +3423,7 @@
         <v>31472.73</v>
       </c>
       <c r="I2">
-        <v>580</v>
+        <v>434</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
